--- a/data/output/2025/evaluasi_63.xlsx
+++ b/data/output/2025/evaluasi_63.xlsx
@@ -18,6 +18,9 @@
     <sheet name="6305" sheetId="9" state="visible" r:id="rId9"/>
     <sheet name="6310" sheetId="10" state="visible" r:id="rId10"/>
     <sheet name="6311" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="6307" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="6308" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="6372" sheetId="14" state="visible" r:id="rId14"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1069,7 +1072,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1129,6 +1132,230 @@
       <c r="F2" t="inlineStr">
         <is>
           <t>Nilai revisi lebih dari (+-4 point) dari nilai rilis</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>6310</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Tanah Bumbu</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>11.38466550459194</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q4-25_prov vs q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>6310</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Tanah Bumbu</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>11.16697237192419</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>6310</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Tanah Bumbu</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q4-25_prov vs y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>6310</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Tanah Bumbu</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>-4.419800125638995</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6310</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Tanah Bumbu</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>3.796639064638544</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q4-25_prov vs y-on-y_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>6310</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Tanah Bumbu</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>-0.4173472848863634</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q4-25_prov vs c-to-c_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>6310</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Tanah Bumbu</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>0.3816603511083845</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pdrb_q4-25_prov vs implisit_q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>6310</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kabupaten Tanah Bumbu</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>0.4860997984030538</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pdrb_q4-25_prov vs implisit_y-on-y_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1370,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1231,6 +1458,1292 @@
       <c r="F3" t="inlineStr">
         <is>
           <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>6311</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Balangan</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>20.8100195209385</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q4-25_prov vs q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>6311</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Balangan</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>-9.072325002690109</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q4-25_prov vs q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>6311</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Balangan</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>32.20459687925833</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6311</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Balangan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>16.69432120232542</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q4-25_prov vs q-to-q_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>6311</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Balangan</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q4-25_prov vs y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>6311</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Balangan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>2.560848186423605</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q4-25_prov vs y-on-y_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>6311</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kabupaten Balangan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>-0.5424769091701337</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>c-to-c_pklnprt_q4-25_prov vs c-to-c_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>6311</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kabupaten Balangan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>0.9442691180663052</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pdrb_q4-25_prov vs implisit_q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>6311</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kabupaten Balangan</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>0.1956182199925382</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pdrb_q4-25_prov vs implisit_y-on-y_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>6307</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kabupaten Hulu Sungai Tengah</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>3.327554443455663</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q4-25_prov vs q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>6307</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Hulu Sungai Tengah</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>-2.95732858104703</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q4-25_prov vs q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>6307</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Hulu Sungai Tengah</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>25.99941549944343</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>6307</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Hulu Sungai Tengah</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>0.4252509695264058</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>y-on-y_pkrt_q4-25_prov vs y-on-y_pkrt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>6307</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Hulu Sungai Tengah</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q4-25_prov vs y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6307</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Hulu Sungai Tengah</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>-3.952810321737837</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>6307</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Hulu Sungai Tengah</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>1.314742170013619</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q4-25_prov vs y-on-y_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>6307</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Hulu Sungai Tengah</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>-2.1982029544148</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>c-to-c_pklnprt_q4-25_prov vs c-to-c_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>6307</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kabupaten Hulu Sungai Tengah</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>-1.274752640796753</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q4-25_prov vs c-to-c_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>6307</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kabupaten Hulu Sungai Tengah</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>-0.4459859547253183</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q4-25_prov vs c-to-c_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>6307</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kabupaten Hulu Sungai Tengah</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>0.1514350847137663</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pdrb_q4-25_prov vs implisit_q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>6307</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Kabupaten Hulu Sungai Tengah</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>2.235179423949594</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pdrb_q4-25_prov vs implisit_y-on-y_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>6308</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kabupaten Hulu Sungai Utara</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>2.420101719701212</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q4-25_prov vs q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>6308</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Hulu Sungai Utara</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>10.8537748263421</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>6308</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Hulu Sungai Utara</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>2.472566207315527</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q4-25_prov vs q-to-q_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>6308</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Hulu Sungai Utara</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q4-25_prov vs y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>6308</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Hulu Sungai Utara</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>-14.78926524342771</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6308</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Hulu Sungai Utara</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>-3.282269763772721</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q4-25_prov vs y-on-y_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>6308</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Hulu Sungai Utara</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>0.610973843088329</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>c-to-c_pklnprt_q4-25_prov vs c-to-c_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>6308</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Hulu Sungai Utara</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>-9.881897914663254</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q4-25_prov vs c-to-c_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>6308</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kabupaten Hulu Sungai Utara</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>0.4636392688255513</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q4-25_prov vs c-to-c_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>6308</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kabupaten Hulu Sungai Utara</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>0.4144975578366359</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pdrb_q4-25_prov vs implisit_q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>6308</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kabupaten Hulu Sungai Utara</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>3.180419660316397</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pdrb_q4-25_prov vs implisit_y-on-y_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>6372</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kota Banjarbaru</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>7.42648984133908</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q4-25_prov vs q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>6372</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kota Banjarbaru</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q4-25_prov vs y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>6372</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kota Banjarbaru</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>-3.789376657303991</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>6372</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kota Banjarbaru</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>-1.88604400949422</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q4-25_prov vs y-on-y_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>6372</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kota Banjarbaru</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>-1.485771707061387</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>c-to-c_pklnprt_q4-25_prov vs c-to-c_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6372</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kota Banjarbaru</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>-1.488428715695844</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q4-25_prov vs c-to-c_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>6372</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kota Banjarbaru</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>0.9253768303365538</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q4-25_prov vs c-to-c_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>6372</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kota Banjarbaru</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>0.1317199146617966</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pdrb_q4-25_prov vs implisit_q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>6372</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kota Banjarbaru</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>2.663644981855138</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pdrb_q4-25_prov vs implisit_y-on-y_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -1245,7 +2758,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1529,6 +3042,230 @@
       <c r="F10" t="inlineStr">
         <is>
           <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>6303</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kabupaten Banjar</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>2.039949232382708</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q4-25_prov vs q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>6303</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kabupaten Banjar</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>11.27445959319306</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>6303</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Kabupaten Banjar</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q4-25_prov vs y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>6303</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Kabupaten Banjar</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>11.14370853293078</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>6303</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Kabupaten Banjar</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>0.7043769954569914</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pdrb_q4-25_prov vs implisit_q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>6303</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Kabupaten Banjar</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>-0.5080658827853424</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkp_q4-25_prov vs implisit_q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>6303</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Kabupaten Banjar</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>2.176210018750875</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pdrb_q4-25_prov vs implisit_y-on-y_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>6303</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Kabupaten Banjar</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>5.982569373683596</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pkrt_q4-25_prov vs implisit_y-on-y_pkrt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
@@ -1543,7 +3280,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1687,6 +3424,258 @@
       <c r="F5" t="inlineStr">
         <is>
           <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>6304</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Barito Kuala</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>1.214013084152471</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q4-25_prov vs q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6304</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Barito Kuala</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>8.848377636136215</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>6304</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Barito Kuala</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q4-25_prov vs y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>6304</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Barito Kuala</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>12.12838002512192</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>6304</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kabupaten Barito Kuala</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>1.97821505566277</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q4-25_prov vs y-on-y_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>6304</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kabupaten Barito Kuala</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>0.6707096621889795</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pdrb_q4-25_prov vs implisit_q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>6304</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kabupaten Barito Kuala</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>-0.2359841170379389</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pmtb_q4-25_prov vs implisit_q-to-q_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>6304</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Kabupaten Barito Kuala</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>2.371012717261667</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pdrb_q4-25_prov vs implisit_y-on-y_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>6304</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Kabupaten Barito Kuala</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>-1.083360385520755</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pmtb_2025_prov vs implisit_y-on-y_pmtb_2025_kab</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -1701,7 +3690,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1789,6 +3778,314 @@
       <c r="F3" t="inlineStr">
         <is>
           <t>Nilai revisi lebih dari (+-30%) dari nilai rilis</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>6371</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kota Banjarmasin</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>3.479276184208265</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q4-25_prov vs q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>6371</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kota Banjarmasin</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>28.70445354806051</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>6371</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kota Banjarmasin</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>13.36861455287563</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q4-25_prov vs q-to-q_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6371</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kota Banjarmasin</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q4-25_prov vs y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>6371</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kota Banjarmasin</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>-21.10410766500851</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>6371</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kota Banjarmasin</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>-5.950174610923868</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q4-25_prov vs y-on-y_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>6371</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kota Banjarmasin</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>-8.503209388046246</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>c-to-c_pklnprt_q4-25_prov vs c-to-c_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>6371</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kota Banjarmasin</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>-11.13939716717889</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q4-25_prov vs c-to-c_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>6371</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kota Banjarmasin</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>-2.91609155017889</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q4-25_prov vs c-to-c_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>6371</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Kota Banjarmasin</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>0.8581225998232901</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pdrb_q4-25_prov vs implisit_q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>6371</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Kota Banjarmasin</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>2.867864206854817</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pdrb_q4-25_prov vs implisit_y-on-y_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -1803,7 +4100,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2087,6 +4384,370 @@
       <c r="F10" t="inlineStr">
         <is>
           <t>Nilai revisi dan nilai rilis beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>6302</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kabupaten Kotabaru</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>1.904604014134524</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q4-25_prov vs q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>6302</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kabupaten Kotabaru</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>5.326103546571033</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>6302</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Kabupaten Kotabaru</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>-56.67225693143981</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q4-25_prov vs q-to-q_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>6302</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Kabupaten Kotabaru</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q4-25_prov vs y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>6302</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Kabupaten Kotabaru</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>-2.246664368297798</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>6302</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Kabupaten Kotabaru</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>41.71759450891845</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q4-25_prov vs y-on-y_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>6302</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Kabupaten Kotabaru</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>-0.1803157588587684</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q4-25_prov vs c-to-c_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>6302</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Kabupaten Kotabaru</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>122.9189866500251</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q4-25_prov vs c-to-c_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>6302</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Kabupaten Kotabaru</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>0.4196028667391091</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pdrb_q4-25_prov vs implisit_q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>6302</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Kabupaten Kotabaru</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>-0.8499999999999973</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkp_q4-25_prov vs implisit_q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>6302</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Kabupaten Kotabaru</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>-12.85085202524743</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pmtb_q4-25_prov vs implisit_q-to-q_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>6302</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Kabupaten Kotabaru</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>2.640870756841267</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pdrb_q4-25_prov vs implisit_y-on-y_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>6302</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Kabupaten Kotabaru</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>-7.775516884394793</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pmtb_q4-25_prov vs implisit_y-on-y_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -2101,7 +4762,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2273,6 +4934,314 @@
       <c r="F6" t="inlineStr">
         <is>
           <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6309</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Tabalong</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>7.197163044491963</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q4-25_prov vs q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>6309</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Tabalong</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>31.60789947598973</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>6309</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Tabalong</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>12.32613535746466</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q4-25_prov vs q-to-q_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>6309</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kabupaten Tabalong</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q4-25_prov vs y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>6309</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kabupaten Tabalong</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>-2.412917999444353</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>c-to-c_pklnprt_q4-25_prov vs c-to-c_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>6309</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kabupaten Tabalong</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>-1.175370174745572</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q4-25_prov vs c-to-c_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>6309</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Kabupaten Tabalong</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>0.798276039060387</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q4-25_prov vs c-to-c_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>6309</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Kabupaten Tabalong</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>1.864066565069196</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pdrb_q4-25_prov vs implisit_q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>6309</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Kabupaten Tabalong</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>-0.6075534132548681</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkp_q4-25_prov vs implisit_q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>6309</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Kabupaten Tabalong</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>0.7065625866627621</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pdrb_q4-25_prov vs implisit_y-on-y_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>6309</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Kabupaten Tabalong</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>5.375118813412802</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pkp_q4-25_prov vs implisit_y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
@@ -2287,7 +5256,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2459,6 +5428,314 @@
       <c r="F6" t="inlineStr">
         <is>
           <t>Nilai revisi dan nilai rilis beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6306</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Hulu Sungai Selatan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>7.500562583392504</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q4-25_prov vs q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>6306</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Hulu Sungai Selatan</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>-0.8959692307458541</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q4-25_prov vs q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>6306</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Hulu Sungai Selatan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>28.45197014398148</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>6306</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kabupaten Hulu Sungai Selatan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q4-25_prov vs y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>6306</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kabupaten Hulu Sungai Selatan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>-3.729531765987848</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>6306</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kabupaten Hulu Sungai Selatan</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>0.4529856853094313</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q4-25_prov vs y-on-y_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>6306</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Kabupaten Hulu Sungai Selatan</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>-1.186844957774576</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>c-to-c_pklnprt_q4-25_prov vs c-to-c_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>6306</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Kabupaten Hulu Sungai Selatan</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>-2.557245273450327</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q4-25_prov vs c-to-c_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>6306</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Kabupaten Hulu Sungai Selatan</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>0.9221568440132921</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q4-25_prov vs c-to-c_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>6306</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Kabupaten Hulu Sungai Selatan</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>0.4398304936201034</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pdrb_q4-25_prov vs implisit_q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>6306</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Kabupaten Hulu Sungai Selatan</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>1.72490354270116</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pdrb_q4-25_prov vs implisit_y-on-y_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -2473,7 +5750,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2617,6 +5894,286 @@
       <c r="F5" t="inlineStr">
         <is>
           <t>Nilai revisi dan nilai rilis beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>6301</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Tanah Laut</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>1.310793349211107</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q4-25_prov vs q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6301</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Tanah Laut</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>5.742013993396585</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>6301</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Tanah Laut</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>-0.152930967168537</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q4-25_prov vs q-to-q_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>6301</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Tanah Laut</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q4-25_prov vs y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>6301</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kabupaten Tanah Laut</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>-1.822544510620698</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>6301</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kabupaten Tanah Laut</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>3.018607810800411</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q4-25_prov vs y-on-y_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>6301</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kabupaten Tanah Laut</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>0.5727887276136174</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pdrb_q4-25_prov vs implisit_q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>6301</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Kabupaten Tanah Laut</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>-1.707039524224864</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkp_q4-25_prov vs implisit_q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>6301</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Kabupaten Tanah Laut</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>-0.03699318642970748</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pmtb_q4-25_prov vs implisit_q-to-q_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>6301</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Kabupaten Tanah Laut</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>2.510392951267069</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pdrb_q4-25_prov vs implisit_y-on-y_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -2631,7 +6188,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2761,18 +6318,354 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>q3-25</t>
+          <t>q4-25</t>
         </is>
       </c>
       <c r="D5" t="n">
+        <v>8.142994333539743</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q4-25_prov vs q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>6305</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Tapin</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>-4.840801981570672</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q4-25_prov vs q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6305</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Tapin</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>15.00000000000001</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>6305</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Tapin</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>-0.3661884705108422</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q4-25_prov vs q-to-q_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>6305</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Tapin</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q4-25_prov vs y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>6305</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kabupaten Tapin</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>1.851456621858815</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q4-25_prov vs y-on-y_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>6305</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kabupaten Tapin</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>0.4003547447552919</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>c-to-c_pklnprt_q4-25_prov vs c-to-c_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>6305</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kabupaten Tapin</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>0.81724908622187</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pdrb_q4-25_prov vs implisit_q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>6305</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Kabupaten Tapin</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>5.357130038636305</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pklnprt_q4-25_prov vs implisit_q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>6305</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Kabupaten Tapin</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>-0.9500416317520053</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkp_q4-25_prov vs implisit_q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>6305</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Kabupaten Tapin</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>-0.02132040462393923</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pmtb_q4-25_prov vs implisit_q-to-q_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>6305</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Kabupaten Tapin</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>2.45003090383796</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pdrb_q4-25_prov vs implisit_y-on-y_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>6305</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Kabupaten Tapin</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
         <v>-2.135935875277819</v>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>sog_y-on-y_pi_2025</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>SoG PI lebih dari +-2 persen</t>
         </is>
